--- a/public/exports-60-250/35209115.xlsx
+++ b/public/exports-60-250/35209115.xlsx
@@ -4391,26 +4391,26 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risingsvej 25</t>
+          <t xml:space="preserve">Roerskov Havekoloni 59</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5474054</t>
+          <t xml:space="preserve">728376, 100159747</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J59">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roerskov Havekoloni 59</t>
+          <t xml:space="preserve">Roesskovsvej 121</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,16 +4476,16 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">728376, 100159747</t>
+          <t xml:space="preserve">9552564</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4541,26 +4541,26 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roesskovsvej 121</t>
+          <t xml:space="preserve">Rosenbækken Havekoloni 200</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552564</t>
+          <t xml:space="preserve">100159748</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J61">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,26 +4616,26 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenbækken Havekoloni 200</t>
+          <t xml:space="preserve">Rødegårdsvej 164</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">100159748</t>
+          <t xml:space="preserve">5466521</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J62">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødegårdsvej 164</t>
+          <t xml:space="preserve">Rødegårdsvej 200</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,16 +4701,16 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5466521</t>
+          <t xml:space="preserve">728472, 5460566</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J63">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødegårdsvej 200</t>
+          <t xml:space="preserve">Rødegårdsvej 315</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,16 +4776,16 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">728472, 5460566</t>
+          <t xml:space="preserve">728314, 5460524</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J64">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4841,26 +4841,26 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødegårdsvej 315</t>
+          <t xml:space="preserve">Sandhusvej 74</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">728314, 5460524</t>
+          <t xml:space="preserve">728196, 9552637</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J65">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4916,26 +4916,26 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandhusvej 74</t>
+          <t xml:space="preserve">Skolevej 9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">728196, 9552637</t>
+          <t xml:space="preserve">2639053</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J66">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5001,16 +5001,16 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2639053</t>
+          <t xml:space="preserve">2640119</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J67">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5066,26 +5066,26 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 9</t>
+          <t xml:space="preserve">Skovsbovænget 7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640119</t>
+          <t xml:space="preserve">9552605</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>95</v>
+        <v>244</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5156,11 +5156,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J69">
-        <v>244</v>
+        <v>130</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovænget 7</t>
+          <t xml:space="preserve">Skovsbovænget 9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5231,11 +5231,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J70">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5291,26 +5291,26 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovænget 9</t>
+          <t xml:space="preserve">Skt. Klemens Vej 97</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552605</t>
+          <t xml:space="preserve">2626977</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J71">
-        <v>183</v>
+        <v>63</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5366,26 +5366,26 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skt. Klemens Vej 97</t>
+          <t xml:space="preserve">Slettensvej 292</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2626977</t>
+          <t xml:space="preserve">1330413</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J72">
-        <v>63</v>
+        <v>186</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,26 +5441,26 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slettensvej 292</t>
+          <t xml:space="preserve">Solbærvej 3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1330413</t>
+          <t xml:space="preserve">9551922</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5516,17 +5516,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbærvej 3</t>
+          <t xml:space="preserve">Sophus Bauditz Vej 29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9551922</t>
+          <t xml:space="preserve">5462452</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="J74">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5591,26 +5591,26 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophus Bauditz Vej 29</t>
+          <t xml:space="preserve">Spurvelundsvej 20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462452</t>
+          <t xml:space="preserve">728438, 2616401</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J75">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="J76">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5741,26 +5741,26 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spurvelundsvej 20</t>
+          <t xml:space="preserve">Stadionvej 43A</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">728438, 2616401</t>
+          <t xml:space="preserve">5458778</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J77">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5831,11 +5831,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J78">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5891,26 +5891,26 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 43A</t>
+          <t xml:space="preserve">Stenløsevej 74A</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5458778</t>
+          <t xml:space="preserve">728213, 100910072</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J79">
-        <v>210</v>
+        <v>96</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5966,26 +5966,26 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenløsevej 74A</t>
+          <t xml:space="preserve">Store Klaus 40</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">728213, 100910072</t>
+          <t xml:space="preserve">10086415</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6056,11 +6056,11 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J81">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6116,26 +6116,26 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Klaus 40</t>
+          <t xml:space="preserve">Stærmosegårdsvej 55B</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">10086415</t>
+          <t xml:space="preserve">5464611</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J82">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,26 +6191,26 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stærmosegårdsvej 55B</t>
+          <t xml:space="preserve">Teglværksvej 15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5464611</t>
+          <t xml:space="preserve">10108552</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J83">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6266,26 +6266,26 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 15</t>
+          <t xml:space="preserve">Thorvalds Vænge 3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">10108552</t>
+          <t xml:space="preserve">728370, 5462460</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J84">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6341,26 +6341,26 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvalds Vænge 3</t>
+          <t xml:space="preserve">Toftevej 65</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">728370, 5462460</t>
+          <t xml:space="preserve">728399, 5464134</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftevej 65</t>
+          <t xml:space="preserve">Toftevej 67</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,16 +6426,16 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">728399, 5464134</t>
+          <t xml:space="preserve">728415, 5464126</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J86">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6491,26 +6491,26 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftevej 67</t>
+          <t xml:space="preserve">Tranevej 44</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">728415, 5464126</t>
+          <t xml:space="preserve">728246, 5473713</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J87">
-        <v>103</v>
+        <v>228</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 44</t>
+          <t xml:space="preserve">Unsbjergvej 30B</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">728246, 5473713</t>
+          <t xml:space="preserve">728413, 2652808</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="J88">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6641,26 +6641,26 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unsbjergvej 30B</t>
+          <t xml:space="preserve">Violvej 16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">728413, 2652808</t>
+          <t xml:space="preserve">5474262</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J89">
-        <v>198</v>
+        <v>90</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,26 +6716,26 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unsgaardsgade 1A</t>
+          <t xml:space="preserve">Volderslevvej 36C</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5475500</t>
+          <t xml:space="preserve">728898, 10104759</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6791,26 +6791,26 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Violvej 16</t>
+          <t xml:space="preserve">Åsumvej 390B</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5474262</t>
+          <t xml:space="preserve">9552546</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J91">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -6866,17 +6866,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volderslevvej 36C</t>
+          <t xml:space="preserve">Øksnebjergvej 15A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">728898, 10104759</t>
+          <t xml:space="preserve">728263, 5471841</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="J92">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6941,26 +6941,26 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åsumvej 390B</t>
+          <t xml:space="preserve">Øksnebjergvej 15C</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552546</t>
+          <t xml:space="preserve">5466913</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7016,17 +7016,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øksnebjergvej 15A</t>
+          <t xml:space="preserve">Østbirkvej 15B</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">728263, 5471841</t>
+          <t xml:space="preserve">728268, 2658873</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="J94">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7091,26 +7091,26 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øksnebjergvej 15C</t>
+          <t xml:space="preserve">Østbirkvej 21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5466913</t>
+          <t xml:space="preserve">9552403, 100696476</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
-        <v>84</v>
+        <v>175</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7166,17 +7166,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østbirkvej 15B</t>
+          <t xml:space="preserve">Østparken 1B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">728268, 2658873</t>
+          <t xml:space="preserve">100561045</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="J96">
-        <v>127</v>
+        <v>225</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7241,26 +7241,26 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østbirkvej 21</t>
+          <t xml:space="preserve">Østre Kanalvej 10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552403, 100696476</t>
+          <t xml:space="preserve">728276, 9552627</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J97">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7316,26 +7316,26 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østparken 1B</t>
+          <t xml:space="preserve">Østre Kanalvej 12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">100561045</t>
+          <t xml:space="preserve">728559, 9552627</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J98">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kanalvej 10</t>
+          <t xml:space="preserve">Østre Kanalvej 18</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,16 +7401,16 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">728276, 9552627</t>
+          <t xml:space="preserve">728277, 9552627</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J99">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kanalvej 12</t>
+          <t xml:space="preserve">Østre Kanalvej 4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,16 +7476,16 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">728559, 9552627</t>
+          <t xml:space="preserve">728275, 9552625</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J100">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7541,45 +7541,45 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kanalvej 18</t>
+          <t xml:space="preserve">Fraugde-Kærby-Vej 106</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">728277, 9552627</t>
+          <t xml:space="preserve">7770782</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100058667</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Just Consult BSK A/S</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2017-12-06</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kanalvej 4</t>
+          <t xml:space="preserve">Bystævnet 17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">728275, 9552625</t>
+          <t xml:space="preserve">2626249</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100104499</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-11-18</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fraugde-Kærby-Vej 106</t>
+          <t xml:space="preserve">Paaskeløkkevej 26</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7770782</t>
+          <t xml:space="preserve">5461723</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,21 +7710,21 @@
         </is>
       </c>
       <c r="J103">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">100058667</t>
+          <t xml:space="preserve">100104505</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Just Consult BSK A/S</t>
+          <t xml:space="preserve">PP Rådgivning A/S</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017-12-06</t>
+          <t xml:space="preserve">2018-11-18</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,30 +7766,30 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bystævnet 17</t>
+          <t xml:space="preserve">Kirkendrupvej 67</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2626249</t>
+          <t xml:space="preserve">2615875</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J104">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">100104499</t>
+          <t xml:space="preserve">100123712</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-11-18</t>
+          <t xml:space="preserve">2019-06-12</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paaskeløkkevej 26</t>
+          <t xml:space="preserve">Fædresmindevej 34</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461723</t>
+          <t xml:space="preserve">2622808</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,21 +7860,21 @@
         </is>
       </c>
       <c r="J105">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">100104505</t>
+          <t xml:space="preserve">100125684</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-11-18</t>
+          <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,40 +7916,40 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkendrupvej 67</t>
+          <t xml:space="preserve">Rugårdsvej 304</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2615875</t>
+          <t xml:space="preserve">2619449</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">100123712</t>
+          <t xml:space="preserve">100125973</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Poul Pedersen, Bygnings- ingeniører og Konsulenter ApS</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-12</t>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,40 +7991,40 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fædresmindevej 34</t>
+          <t xml:space="preserve">Kløvermosevej 91</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2622808</t>
+          <t xml:space="preserve">728150, 10088928</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J107">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">100125684</t>
+          <t xml:space="preserve">200045405</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-29</t>
+          <t xml:space="preserve">2021-02-09</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,40 +8066,40 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugårdsvej 304</t>
+          <t xml:space="preserve">Møllemarksvej 84</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2619449</t>
+          <t xml:space="preserve">728377, 10088928</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="J108">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100125973</t>
+          <t xml:space="preserve">200045405</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poul Pedersen, Bygnings- ingeniører og Konsulenter ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2021-02-09</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,30 +8141,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermosevej 91</t>
+          <t xml:space="preserve">Niels Bohrs Allé 148B</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">728150, 10088928</t>
+          <t xml:space="preserve">728446, 9552534</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>237</v>
+        <v>89</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045405</t>
+          <t xml:space="preserve">200045414</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,40 +8216,40 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemarksvej 84</t>
+          <t xml:space="preserve">Ørbækvej 701</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">728377, 10088928</t>
+          <t xml:space="preserve">2650774</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J110">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045405</t>
+          <t xml:space="preserve">200052073</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-09</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,17 +8291,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Bohrs Allé 148B</t>
+          <t xml:space="preserve">Brændekildevej 32</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">728446, 9552534</t>
+          <t xml:space="preserve">2606523</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,21 +8310,21 @@
         </is>
       </c>
       <c r="J111">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045414</t>
+          <t xml:space="preserve">200056389</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-09</t>
+          <t xml:space="preserve">2022-01-02</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risingsvej 25A</t>
+          <t xml:space="preserve">Dalumvej 106</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5474054</t>
+          <t xml:space="preserve">9551907</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J112">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049879</t>
+          <t xml:space="preserve">200057384</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-06</t>
+          <t xml:space="preserve">2022-02-13</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,30 +8441,30 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørbækvej 701</t>
+          <t xml:space="preserve">Skibhusvej 196</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650774</t>
+          <t xml:space="preserve">5472449</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052073</t>
+          <t xml:space="preserve">200057787</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-18</t>
+          <t xml:space="preserve">2022-02-28</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændekildevej 32</t>
+          <t xml:space="preserve">Egebæksvej 22</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2606523</t>
+          <t xml:space="preserve">5472285</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056389</t>
+          <t xml:space="preserve">200058297</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-01-02</t>
+          <t xml:space="preserve">2022-03-22</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalumvej 106</t>
+          <t xml:space="preserve">Ejby Kirkevej 25</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9551907</t>
+          <t xml:space="preserve">728897, 5466128</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J115">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057384</t>
+          <t xml:space="preserve">200058295</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-13</t>
+          <t xml:space="preserve">2022-03-22</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skibhusvej 196</t>
+          <t xml:space="preserve">Hans Jensens Stræde 20</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5472449</t>
+          <t xml:space="preserve">8025380</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057787</t>
+          <t xml:space="preserve">100265642</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-28</t>
+          <t xml:space="preserve">2022-04-23</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,30 +8741,30 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egebæksvej 22</t>
+          <t xml:space="preserve">Hollufgårdsvej 167</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5472285</t>
+          <t xml:space="preserve">2651687</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J117">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058297</t>
+          <t xml:space="preserve">200059464</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-03-22</t>
+          <t xml:space="preserve">2022-05-10</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Kirkevej 25</t>
+          <t xml:space="preserve">Hollufgårdsvej 169</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">728897, 5466128</t>
+          <t xml:space="preserve">2651687</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J118">
-        <v>85</v>
+        <v>201</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058295</t>
+          <t xml:space="preserve">200059465</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-03-22</t>
+          <t xml:space="preserve">2022-05-10</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Jensens Stræde 20</t>
+          <t xml:space="preserve">Skibhusvej 388</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8025380</t>
+          <t xml:space="preserve">9552639</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,11 +8910,11 @@
         </is>
       </c>
       <c r="J119">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">100265642</t>
+          <t xml:space="preserve">200061067</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-23</t>
+          <t xml:space="preserve">2022-08-02</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollufgårdsvej 167</t>
+          <t xml:space="preserve">Munkemøllestræde 3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651687</t>
+          <t xml:space="preserve">5453043</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059464</t>
+          <t xml:space="preserve">310004856</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-10</t>
+          <t xml:space="preserve">2022-09-18</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollufgårdsvej 169</t>
+          <t xml:space="preserve">Roesskovsvej 38</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651687</t>
+          <t xml:space="preserve">8194450</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="J121">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059465</t>
+          <t xml:space="preserve">310013009</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-10</t>
+          <t xml:space="preserve">2022-11-12</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,30 +9116,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skibhusvej 388</t>
+          <t xml:space="preserve">Roesskovsvej 40</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552639</t>
+          <t xml:space="preserve">8194450</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J122">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200061067</t>
+          <t xml:space="preserve">310013008</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-08-02</t>
+          <t xml:space="preserve">2022-11-12</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkemøllestræde 3</t>
+          <t xml:space="preserve">Johannes Larsens Vej 1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5453043</t>
+          <t xml:space="preserve">5464137</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="J123">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">310004856</t>
+          <t xml:space="preserve">310015846</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-09-18</t>
+          <t xml:space="preserve">2022-12-03</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roesskovsvej 38</t>
+          <t xml:space="preserve">Cecilievej 4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194450</t>
+          <t xml:space="preserve">2664378</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">310013009</t>
+          <t xml:space="preserve">310017587</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-12</t>
+          <t xml:space="preserve">2022-12-15</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,40 +9341,40 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roesskovsvej 40</t>
+          <t xml:space="preserve">Fruens Bøge Skov 2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194450</t>
+          <t xml:space="preserve">7550963</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">310013008</t>
+          <t xml:space="preserve">310017593</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-12</t>
+          <t xml:space="preserve">2022-12-15</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Larsens Vej 1</t>
+          <t xml:space="preserve">Ryttervejen 21</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5464137</t>
+          <t xml:space="preserve">2650223</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,21 +9435,21 @@
         </is>
       </c>
       <c r="J126">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">310015846</t>
+          <t xml:space="preserve">310023892</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-12-03</t>
+          <t xml:space="preserve">2023-02-06</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cecilievej 4</t>
+          <t xml:space="preserve">Bækholmen 90</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2664378</t>
+          <t xml:space="preserve">2659052</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">310017587</t>
+          <t xml:space="preserve">310027902</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-12-15</t>
+          <t xml:space="preserve">2023-03-04</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fruens Bøge Skov 2</t>
+          <t xml:space="preserve">Hjallesegade 4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550963</t>
+          <t xml:space="preserve">2611856</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="J128">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">310017593</t>
+          <t xml:space="preserve">310027898</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-12-15</t>
+          <t xml:space="preserve">2023-03-04</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttervejen 21</t>
+          <t xml:space="preserve">Krogsløkkeparken 4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650223</t>
+          <t xml:space="preserve">10158269</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,21 +9660,21 @@
         </is>
       </c>
       <c r="J129">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023892</t>
+          <t xml:space="preserve">310027900</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-06</t>
+          <t xml:space="preserve">2023-03-04</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,30 +9716,30 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækholmen 90</t>
+          <t xml:space="preserve">Ravnebjerggyden 78B</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5491</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2659052</t>
+          <t xml:space="preserve">2622594</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J130">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">310027902</t>
+          <t xml:space="preserve">310028023</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjallesegade 4</t>
+          <t xml:space="preserve">Åvangsvej 11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2611856</t>
+          <t xml:space="preserve">5460459</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">310027898</t>
+          <t xml:space="preserve">310027971</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogsløkkeparken 4</t>
+          <t xml:space="preserve">Beldringevej 85</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">10158269</t>
+          <t xml:space="preserve">2661861</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,21 +9885,21 @@
         </is>
       </c>
       <c r="J132">
-        <v>218</v>
+        <v>88</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">310027900</t>
+          <t xml:space="preserve">310028159</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-04</t>
+          <t xml:space="preserve">2023-03-05</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,30 +9941,30 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnebjerggyden 78B</t>
+          <t xml:space="preserve">Brændekildevej 40</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2622594</t>
+          <t xml:space="preserve">2606524</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J133">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028023</t>
+          <t xml:space="preserve">310028659</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-04</t>
+          <t xml:space="preserve">2023-03-07</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åvangsvej 11</t>
+          <t xml:space="preserve">Kærbygårdevej 10</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5460459</t>
+          <t xml:space="preserve">2651618</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">310027971</t>
+          <t xml:space="preserve">310028542</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-04</t>
+          <t xml:space="preserve">2023-03-07</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beldringevej 85</t>
+          <t xml:space="preserve">Londongade 10</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2661861</t>
+          <t xml:space="preserve">9770248</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10110,11 +10110,11 @@
         </is>
       </c>
       <c r="J135">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028159</t>
+          <t xml:space="preserve">310028656</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-05</t>
+          <t xml:space="preserve">2023-03-07</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,30 +10166,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændekildevej 40</t>
+          <t xml:space="preserve">Steinsgade 17B</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2606524</t>
+          <t xml:space="preserve">5475482</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028659</t>
+          <t xml:space="preserve">310028597</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærbygårdevej 10</t>
+          <t xml:space="preserve">Langekærvej 10B</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651618</t>
+          <t xml:space="preserve">2615330</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10260,11 +10260,11 @@
         </is>
       </c>
       <c r="J137">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028542</t>
+          <t xml:space="preserve">310031064</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-07</t>
+          <t xml:space="preserve">2023-03-20</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Londongade 10</t>
+          <t xml:space="preserve">Ubberudvej 31</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5491</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9770248</t>
+          <t xml:space="preserve">2632273</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,11 +10335,11 @@
         </is>
       </c>
       <c r="J138">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028656</t>
+          <t xml:space="preserve">310031062</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-07</t>
+          <t xml:space="preserve">2023-03-20</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,17 +10391,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steinsgade 17B</t>
+          <t xml:space="preserve">Fraugde Byvej 22</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5475482</t>
+          <t xml:space="preserve">2651180</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10410,11 +10410,11 @@
         </is>
       </c>
       <c r="J139">
-        <v>86</v>
+        <v>204</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028597</t>
+          <t xml:space="preserve">310031707</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-07</t>
+          <t xml:space="preserve">2023-03-22</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,30 +10466,30 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langekærvej 10B</t>
+          <t xml:space="preserve">Paarupvej 19</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2615330</t>
+          <t xml:space="preserve">7040245</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J140">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">310031064</t>
+          <t xml:space="preserve">310033866</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-20</t>
+          <t xml:space="preserve">2023-04-08</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ubberudvej 31</t>
+          <t xml:space="preserve">Kochsgade 16</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2632273</t>
+          <t xml:space="preserve">5475447</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="J141">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">310031062</t>
+          <t xml:space="preserve">310040983</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-20</t>
+          <t xml:space="preserve">2023-05-22</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,17 +10616,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fraugde Byvej 22</t>
+          <t xml:space="preserve">Strandvejen 58</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651180</t>
+          <t xml:space="preserve">2658708</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="J142">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">310031707</t>
+          <t xml:space="preserve">311003376</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-03-22</t>
+          <t xml:space="preserve">2023-06-12</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,40 +10691,40 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paarupvej 19</t>
+          <t xml:space="preserve">Alexandragade 2R</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7040245</t>
+          <t xml:space="preserve">5452527</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">310033866</t>
+          <t xml:space="preserve">311004554</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-08</t>
+          <t xml:space="preserve">2023-06-19</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kochsgade 16</t>
+          <t xml:space="preserve">Skt. Klemens Vej 97</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5475447</t>
+          <t xml:space="preserve">2626977</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">310040983</t>
+          <t xml:space="preserve">311011289</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-22</t>
+          <t xml:space="preserve">2023-08-07</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 58</t>
+          <t xml:space="preserve">Friggasvej 14B</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2658708</t>
+          <t xml:space="preserve">728400, 5464020</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J145">
-        <v>221</v>
+        <v>90</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311003376</t>
+          <t xml:space="preserve">311018709</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-12</t>
+          <t xml:space="preserve">2023-09-24</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,40 +10916,40 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandragade 2R</t>
+          <t xml:space="preserve">Friggasvej 14B</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5452527</t>
+          <t xml:space="preserve">728400, 5464020</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J146">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311004554</t>
+          <t xml:space="preserve">311018709</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-19</t>
+          <t xml:space="preserve">2023-09-24</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skt. Klemens Vej 97</t>
+          <t xml:space="preserve">Bjørnemosevej 37B</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2626977</t>
+          <t xml:space="preserve">10087652</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311011289</t>
+          <t xml:space="preserve">311019114</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-07</t>
+          <t xml:space="preserve">2023-09-26</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friggasvej 14B</t>
+          <t xml:space="preserve">Beldringevej 203</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">728400, 5464020</t>
+          <t xml:space="preserve">2661908</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311018709</t>
+          <t xml:space="preserve">311027789</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-09-24</t>
+          <t xml:space="preserve">2023-11-21</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friggasvej 14B</t>
+          <t xml:space="preserve">Beldringevej 203</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">728400, 5464020</t>
+          <t xml:space="preserve">2661908</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J149">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311018709</t>
+          <t xml:space="preserve">311027789</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-09-24</t>
+          <t xml:space="preserve">2023-11-21</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,40 +11216,40 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnemosevej 37B</t>
+          <t xml:space="preserve">Bryllevej 20</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">10087652</t>
+          <t xml:space="preserve">2608005</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J150">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311019114</t>
+          <t xml:space="preserve">311031771</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-09-26</t>
+          <t xml:space="preserve">2023-12-19</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,40 +11291,40 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beldringevej 203</t>
+          <t xml:space="preserve">Bryllevej 20</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2661908</t>
+          <t xml:space="preserve">2608005</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J151">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311027789</t>
+          <t xml:space="preserve">311031771</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-11-21</t>
+          <t xml:space="preserve">2023-12-19</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,40 +11366,40 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beldringevej 203</t>
+          <t xml:space="preserve">Bryllevej 20</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2661908</t>
+          <t xml:space="preserve">2608005</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J152">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311027789</t>
+          <t xml:space="preserve">311031771</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-11-21</t>
+          <t xml:space="preserve">2023-12-19</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J153">
@@ -11516,40 +11516,40 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryllevej 20</t>
+          <t xml:space="preserve">Victoriagade 27A</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608005</t>
+          <t xml:space="preserve">728252, 5472347</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031771</t>
+          <t xml:space="preserve">311178833</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">TREFOR Energi A/S</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-12-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,40 +11591,40 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryllevej 20</t>
+          <t xml:space="preserve">Rugårdsvej 291</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608005</t>
+          <t xml:space="preserve">9552045</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J155">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031771</t>
+          <t xml:space="preserve">311203974</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">TREFOR Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-12-19</t>
+          <t xml:space="preserve">2026-10-02</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,50 +11666,50 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryllevej 20</t>
+          <t xml:space="preserve">Njalsvej 10</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608005</t>
+          <t xml:space="preserve">5462466</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031771</t>
+          <t xml:space="preserve">311216721</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">TREFOR Energi A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-12-19</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Victoriagade 27A</t>
+          <t xml:space="preserve">Njalsvej 168</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">728252, 5472347</t>
+          <t xml:space="preserve">5462544</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,31 +11760,31 @@
         </is>
       </c>
       <c r="J157">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178833</t>
+          <t xml:space="preserve">311216725</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugårdsvej 291</t>
+          <t xml:space="preserve">Njalsvej 6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,30 +11826,30 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552045</t>
+          <t xml:space="preserve">5462464</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203974</t>
+          <t xml:space="preserve">311216719</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02</t>
+          <t xml:space="preserve">2026-12-08</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 10</t>
+          <t xml:space="preserve">Njalsvej 103</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462466</t>
+          <t xml:space="preserve">5462647</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216721</t>
+          <t xml:space="preserve">311217357</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 168</t>
+          <t xml:space="preserve">Njalsvej 129</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462544</t>
+          <t xml:space="preserve">5462627</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216725</t>
+          <t xml:space="preserve">311217358</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 6</t>
+          <t xml:space="preserve">Njalsvej 14</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462464</t>
+          <t xml:space="preserve">5462468</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216719</t>
+          <t xml:space="preserve">311217335</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-08</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 103</t>
+          <t xml:space="preserve">Njalsvej 167</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462647</t>
+          <t xml:space="preserve">5462612</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217357</t>
+          <t xml:space="preserve">311217362</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 129</t>
+          <t xml:space="preserve">Njalsvej 171</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462627</t>
+          <t xml:space="preserve">5462614</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217358</t>
+          <t xml:space="preserve">311217363</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 14</t>
+          <t xml:space="preserve">Njalsvej 20</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462468</t>
+          <t xml:space="preserve">5462471</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217335</t>
+          <t xml:space="preserve">311217341</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 167</t>
+          <t xml:space="preserve">Njalsvej 218</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462612</t>
+          <t xml:space="preserve">5462569</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217362</t>
+          <t xml:space="preserve">311217367</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 171</t>
+          <t xml:space="preserve">Njalsvej 222</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462614</t>
+          <t xml:space="preserve">5462571</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217363</t>
+          <t xml:space="preserve">311217368</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 20</t>
+          <t xml:space="preserve">Njalsvej 228</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462471</t>
+          <t xml:space="preserve">5462574</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217341</t>
+          <t xml:space="preserve">311217369</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 218</t>
+          <t xml:space="preserve">Njalsvej 236</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462569</t>
+          <t xml:space="preserve">5462578</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217367</t>
+          <t xml:space="preserve">311217370</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 222</t>
+          <t xml:space="preserve">Njalsvej 238</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462571</t>
+          <t xml:space="preserve">5462579</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217368</t>
+          <t xml:space="preserve">311217371</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 228</t>
+          <t xml:space="preserve">Njalsvej 32</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462574</t>
+          <t xml:space="preserve">5462477</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217369</t>
+          <t xml:space="preserve">311217343</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 236</t>
+          <t xml:space="preserve">Njalsvej 39</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462578</t>
+          <t xml:space="preserve">5462673</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217370</t>
+          <t xml:space="preserve">311217349</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 238</t>
+          <t xml:space="preserve">Njalsvej 42</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462579</t>
+          <t xml:space="preserve">5462482</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217371</t>
+          <t xml:space="preserve">311217351</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 32</t>
+          <t xml:space="preserve">Njalsvej 61</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462477</t>
+          <t xml:space="preserve">5462659</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217343</t>
+          <t xml:space="preserve">311217356</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 39</t>
+          <t xml:space="preserve">Saxovej 134</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462673</t>
+          <t xml:space="preserve">5462735</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217349</t>
+          <t xml:space="preserve">311217376</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 42</t>
+          <t xml:space="preserve">Saxovej 180</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462482</t>
+          <t xml:space="preserve">5462758</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217351</t>
+          <t xml:space="preserve">311217378</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Njalsvej 61</t>
+          <t xml:space="preserve">Saxovej 198</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462659</t>
+          <t xml:space="preserve">5462767</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217356</t>
+          <t xml:space="preserve">311217381</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saxovej 134</t>
+          <t xml:space="preserve">Edvard Weies Vænge 28</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462735</t>
+          <t xml:space="preserve">5465267</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -13260,11 +13260,11 @@
         </is>
       </c>
       <c r="J177">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217376</t>
+          <t xml:space="preserve">311225274</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,17 +13316,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saxovej 180</t>
+          <t xml:space="preserve">Edvard Weies Vænge 31</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462758</t>
+          <t xml:space="preserve">5465278</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -13335,11 +13335,11 @@
         </is>
       </c>
       <c r="J178">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217378</t>
+          <t xml:space="preserve">311225285</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,17 +13391,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saxovej 198</t>
+          <t xml:space="preserve">Edvard Weies Vænge 39</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462767</t>
+          <t xml:space="preserve">5465282</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,11 +13410,11 @@
         </is>
       </c>
       <c r="J179">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217381</t>
+          <t xml:space="preserve">311225286</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edvard Weies Vænge 28</t>
+          <t xml:space="preserve">Edvard Weies Vænge 4</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465267</t>
+          <t xml:space="preserve">5465255</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,11 +13485,11 @@
         </is>
       </c>
       <c r="J180">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225274</t>
+          <t xml:space="preserve">311225282</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edvard Weies Vænge 31</t>
+          <t xml:space="preserve">Edvard Weies Vænge 9</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465278</t>
+          <t xml:space="preserve">5465165</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225285</t>
+          <t xml:space="preserve">311225278</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,17 +13616,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edvard Weies Vænge 39</t>
+          <t xml:space="preserve">Erholmvænget 25</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465282</t>
+          <t xml:space="preserve">5469368</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,11 +13635,11 @@
         </is>
       </c>
       <c r="J182">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225286</t>
+          <t xml:space="preserve">311225288</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,17 +13691,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edvard Weies Vænge 4</t>
+          <t xml:space="preserve">Erholmvænget 37</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465255</t>
+          <t xml:space="preserve">5469374</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="J183">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225282</t>
+          <t xml:space="preserve">311225291</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edvard Weies Vænge 9</t>
+          <t xml:space="preserve">Giersingvænget 1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465165</t>
+          <t xml:space="preserve">5465167</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225278</t>
+          <t xml:space="preserve">311225442</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erholmvænget 25</t>
+          <t xml:space="preserve">Giersingvænget 12</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469368</t>
+          <t xml:space="preserve">5465287</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225288</t>
+          <t xml:space="preserve">311225450</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13916,17 +13916,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erholmvænget 37</t>
+          <t xml:space="preserve">Giersingvænget 19</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469374</t>
+          <t xml:space="preserve">5465308</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225291</t>
+          <t xml:space="preserve">311225456</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giersingvænget 1</t>
+          <t xml:space="preserve">Giersingvænget 2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465167</t>
+          <t xml:space="preserve">5465292</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225442</t>
+          <t xml:space="preserve">311225444</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giersingvænget 12</t>
+          <t xml:space="preserve">Giersingvænget 23</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465287</t>
+          <t xml:space="preserve">5465310</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225450</t>
+          <t xml:space="preserve">311225460</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giersingvænget 19</t>
+          <t xml:space="preserve">Giersingvænget 6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465308</t>
+          <t xml:space="preserve">5465290</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225456</t>
+          <t xml:space="preserve">311225446</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giersingvænget 2</t>
+          <t xml:space="preserve">Giersingvænget 7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465292</t>
+          <t xml:space="preserve">5465170</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225444</t>
+          <t xml:space="preserve">311225447</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14291,17 +14291,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giersingvænget 23</t>
+          <t xml:space="preserve">Hesbjergvænget 43</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465310</t>
+          <t xml:space="preserve">5469425</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225460</t>
+          <t xml:space="preserve">311225302</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14366,17 +14366,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giersingvænget 6</t>
+          <t xml:space="preserve">Krengerupvænget 14</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465290</t>
+          <t xml:space="preserve">5469488</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225446</t>
+          <t xml:space="preserve">311225397</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giersingvænget 7</t>
+          <t xml:space="preserve">Krengerupvænget 24</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465170</t>
+          <t xml:space="preserve">5469493</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225447</t>
+          <t xml:space="preserve">311225403</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hesbjergvænget 43</t>
+          <t xml:space="preserve">Krengerupvænget 3</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469425</t>
+          <t xml:space="preserve">5469453</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225302</t>
+          <t xml:space="preserve">311225380</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krengerupvænget 14</t>
+          <t xml:space="preserve">Krengerupvænget 39</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469488</t>
+          <t xml:space="preserve">5469471</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225397</t>
+          <t xml:space="preserve">311225406</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krengerupvænget 24</t>
+          <t xml:space="preserve">Krengerupvænget 43</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469493</t>
+          <t xml:space="preserve">5469473</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225403</t>
+          <t xml:space="preserve">311225412</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krengerupvænget 3</t>
+          <t xml:space="preserve">Krengerupvænget 44</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469453</t>
+          <t xml:space="preserve">5469503</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225380</t>
+          <t xml:space="preserve">311225415</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14816,17 +14816,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krengerupvænget 39</t>
+          <t xml:space="preserve">Larsen Stevns Vænge 11</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469471</t>
+          <t xml:space="preserve">5465154</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225406</t>
+          <t xml:space="preserve">311225425</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krengerupvænget 43</t>
+          <t xml:space="preserve">Larsen Stevns Vænge 16</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469473</t>
+          <t xml:space="preserve">5465195</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225412</t>
+          <t xml:space="preserve">311225430</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krengerupvænget 44</t>
+          <t xml:space="preserve">Larsen Stevns Vænge 33</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5469503</t>
+          <t xml:space="preserve">5465213</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14989,7 +14989,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225415</t>
+          <t xml:space="preserve">311225433</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larsen Stevns Vænge 11</t>
+          <t xml:space="preserve">Larsen Stevns Vænge 6</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465154</t>
+          <t xml:space="preserve">5465188</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,11 +15060,11 @@
         </is>
       </c>
       <c r="J201">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225425</t>
+          <t xml:space="preserve">311225420</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larsen Stevns Vænge 16</t>
+          <t xml:space="preserve">Larsen Stevns Vænge 7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465195</t>
+          <t xml:space="preserve">5465152</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225430</t>
+          <t xml:space="preserve">311225421</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larsen Stevns Vænge 33</t>
+          <t xml:space="preserve">Larsen Stevns Vænge 8</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465213</t>
+          <t xml:space="preserve">5465187</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225433</t>
+          <t xml:space="preserve">311225422</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larsen Stevns Vænge 6</t>
+          <t xml:space="preserve">Sybergsvej 17</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465188</t>
+          <t xml:space="preserve">5465127</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225420</t>
+          <t xml:space="preserve">311225331</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larsen Stevns Vænge 7</t>
+          <t xml:space="preserve">Sybergsvej 41</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465152</t>
+          <t xml:space="preserve">5465139</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225421</t>
+          <t xml:space="preserve">311225352</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larsen Stevns Vænge 8</t>
+          <t xml:space="preserve">Sybergsvej 47</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465187</t>
+          <t xml:space="preserve">5465142</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -15435,11 +15435,11 @@
         </is>
       </c>
       <c r="J206">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225422</t>
+          <t xml:space="preserve">311225369</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sybergsvej 17</t>
+          <t xml:space="preserve">Sybergsvej 5</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465127</t>
+          <t xml:space="preserve">5465121</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225331</t>
+          <t xml:space="preserve">311225304</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sybergsvej 41</t>
+          <t xml:space="preserve">Brejdablik 36</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465139</t>
+          <t xml:space="preserve">2651568</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,21 +15585,21 @@
         </is>
       </c>
       <c r="J208">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225352</t>
+          <t xml:space="preserve">311225925</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sybergsvej 47</t>
+          <t xml:space="preserve">Over-Holluf-Vej 4</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465142</t>
+          <t xml:space="preserve">2653067</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,11 +15660,11 @@
         </is>
       </c>
       <c r="J209">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225369</t>
+          <t xml:space="preserve">311225897</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,17 +15716,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sybergsvej 5</t>
+          <t xml:space="preserve">Rullekrovej 21</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465121</t>
+          <t xml:space="preserve">2663932</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,11 +15735,11 @@
         </is>
       </c>
       <c r="J210">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225306</t>
+          <t xml:space="preserve">311225887</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,17 +15791,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brejdablik 36</t>
+          <t xml:space="preserve">H.J. Poulsens Allé 126</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651568</t>
+          <t xml:space="preserve">2623620</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,21 +15810,21 @@
         </is>
       </c>
       <c r="J211">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225925</t>
+          <t xml:space="preserve">311228856</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-02-16</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,17 +15866,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Over-Holluf-Vej 4</t>
+          <t xml:space="preserve">Paaskeløkkevej 27</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2653067</t>
+          <t xml:space="preserve">5461738</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,11 +15885,11 @@
         </is>
       </c>
       <c r="J212">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225897</t>
+          <t xml:space="preserve">311229449</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-02-20</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,17 +15941,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rullekrovej 21</t>
+          <t xml:space="preserve">Paaskeløkkevej 40</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2663932</t>
+          <t xml:space="preserve">5461730</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15960,11 +15960,11 @@
         </is>
       </c>
       <c r="J213">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225887</t>
+          <t xml:space="preserve">311229434</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-02-20</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,17 +16016,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.J. Poulsens Allé 126</t>
+          <t xml:space="preserve">Roersvej 6</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2623620</t>
+          <t xml:space="preserve">5454018</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,11 +16035,11 @@
         </is>
       </c>
       <c r="J214">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311228856</t>
+          <t xml:space="preserve">311229959</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-16</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paaskeløkkevej 27</t>
+          <t xml:space="preserve">Vendersvej 5</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461738</t>
+          <t xml:space="preserve">5461756</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229449</t>
+          <t xml:space="preserve">311229939</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-20</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paaskeløkkevej 40</t>
+          <t xml:space="preserve">Arkonavej 13</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461730</t>
+          <t xml:space="preserve">5461810</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229434</t>
+          <t xml:space="preserve">311230175</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-20</t>
+          <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roersvej 6</t>
+          <t xml:space="preserve">Arkonavej 2</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5454018</t>
+          <t xml:space="preserve">5461797</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -16260,11 +16260,11 @@
         </is>
       </c>
       <c r="J217">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229959</t>
+          <t xml:space="preserve">311230183</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,17 +16316,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersvej 5</t>
+          <t xml:space="preserve">Niels Bjerres Vænge 19</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461756</t>
+          <t xml:space="preserve">5465236</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -16335,11 +16335,11 @@
         </is>
       </c>
       <c r="J218">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229939</t>
+          <t xml:space="preserve">311230248</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,17 +16391,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arkonavej 13</t>
+          <t xml:space="preserve">Niels Bjerres Vænge 27</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461810</t>
+          <t xml:space="preserve">5465240</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230175</t>
+          <t xml:space="preserve">311230247</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16466,17 +16466,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arkonavej 2</t>
+          <t xml:space="preserve">Niels Bjerres Vænge 29</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461797</t>
+          <t xml:space="preserve">5465241</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,11 +16485,11 @@
         </is>
       </c>
       <c r="J220">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230183</t>
+          <t xml:space="preserve">311230245</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Bjerres Vænge 19</t>
+          <t xml:space="preserve">Niels Bjerres Vænge 36</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465236</t>
+          <t xml:space="preserve">5465227</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230248</t>
+          <t xml:space="preserve">311230244</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Bjerres Vænge 27</t>
+          <t xml:space="preserve">Nyborgvej 689</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465240</t>
+          <t xml:space="preserve">2651575</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,21 +16635,21 @@
         </is>
       </c>
       <c r="J222">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230247</t>
+          <t xml:space="preserve">311266318</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-23</t>
+          <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Bjerres Vænge 29</t>
+          <t xml:space="preserve">Fraugde-Kærby-Vej 96</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465241</t>
+          <t xml:space="preserve">8232693</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,21 +16710,21 @@
         </is>
       </c>
       <c r="J223">
-        <v>89</v>
+        <v>203</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230245</t>
+          <t xml:space="preserve">311285556</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">Botjek Center Fyn</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-23</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,40 +16766,40 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Bjerres Vænge 36</t>
+          <t xml:space="preserve">Stadionvej 50N</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465227</t>
+          <t xml:space="preserve">5458558, 100347898</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J224">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230244</t>
+          <t xml:space="preserve">311298969</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-23</t>
+          <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,30 +16841,30 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyborgvej 689</t>
+          <t xml:space="preserve">Mågebakken 199R</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651575</t>
+          <t xml:space="preserve">2622776</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="J225">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266318</t>
+          <t xml:space="preserve">311431171</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-15</t>
+          <t xml:space="preserve">2030-04-01</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,17 +16916,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fraugde-Kærby-Vej 96</t>
+          <t xml:space="preserve">Rugårdsvej 321</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">8232693</t>
+          <t xml:space="preserve">7106874</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16935,21 +16935,21 @@
         </is>
       </c>
       <c r="J226">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285556</t>
+          <t xml:space="preserve">311463578</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Center Fyn</t>
+          <t xml:space="preserve">BMH Rådgivning ApS</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2030-09-26</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 50N</t>
+          <t xml:space="preserve">Stadionvej 50A</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,30 +17001,30 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5458558, 100347898</t>
+          <t xml:space="preserve">5458558</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J227">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298969</t>
+          <t xml:space="preserve">311630097</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-21</t>
+          <t xml:space="preserve">2032-09-22</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,40 +17066,40 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mågebakken 199R</t>
+          <t xml:space="preserve">Overgade 44</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2622776</t>
+          <t xml:space="preserve">5456150</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J228">
-        <v>62</v>
+        <v>215</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311431171</t>
+          <t xml:space="preserve">311646432</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-01</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,17 +17141,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugårdsvej 321</t>
+          <t xml:space="preserve">Vindegade 7</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">7106874</t>
+          <t xml:space="preserve">5455148</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,21 +17160,21 @@
         </is>
       </c>
       <c r="J229">
-        <v>219</v>
+        <v>109</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311463578</t>
+          <t xml:space="preserve">311660563</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">BMH Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-26</t>
+          <t xml:space="preserve">2033-02-16</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,40 +17216,40 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 50A</t>
+          <t xml:space="preserve">Ørbækvej 100A</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5458558</t>
+          <t xml:space="preserve">5464606</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J230">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311630097</t>
+          <t xml:space="preserve">311665841</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-22</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,40 +17291,40 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 44</t>
+          <t xml:space="preserve">Ørbækvej 100A</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5456150</t>
+          <t xml:space="preserve">5464606</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J231">
-        <v>215</v>
+        <v>121</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646432</t>
+          <t xml:space="preserve">311665841</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,17 +17366,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegade 7</t>
+          <t xml:space="preserve">Sanderumvej 269</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5455148</t>
+          <t xml:space="preserve">10175742</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,21 +17385,21 @@
         </is>
       </c>
       <c r="J232">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660563</t>
+          <t xml:space="preserve">311679120</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-16</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørbækvej 100A</t>
+          <t xml:space="preserve">Brejdablik 28</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,30 +17451,30 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5464606</t>
+          <t xml:space="preserve">2651570</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665841</t>
+          <t xml:space="preserve">311696470</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2033-07-24</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17511,45 +17511,45 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">430</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørbækvej 100A</t>
+          <t xml:space="preserve">Boltinggårdvej 1</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5750</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5464606</t>
+          <t xml:space="preserve">3028255</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J234">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665841</t>
+          <t xml:space="preserve">311789683</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Rydahl Byggesagkyndig</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2034-10-06</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,17 +17591,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sanderumvej 269</t>
+          <t xml:space="preserve">Spurvelundsvej 10</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">10175742</t>
+          <t xml:space="preserve">2616401</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -17610,21 +17610,21 @@
         </is>
       </c>
       <c r="J235">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679120</t>
+          <t xml:space="preserve">311801762</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2034-12-09</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,40 +17666,40 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brejdablik 28</t>
+          <t xml:space="preserve">Møllemarksvej 43</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651570</t>
+          <t xml:space="preserve">286845</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696470</t>
+          <t xml:space="preserve">311843430</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-24</t>
+          <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17736,45 +17736,45 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">430</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boltinggårdvej 1</t>
+          <t xml:space="preserve">Nørrelunden 20</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5750</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">3028255</t>
+          <t xml:space="preserve">2654536</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J237">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311789683</t>
+          <t xml:space="preserve">311843436</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rydahl Byggesagkyndig</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-06</t>
+          <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,40 +17816,40 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spurvelundsvej 10</t>
+          <t xml:space="preserve">Nørrelunden 20</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2616401</t>
+          <t xml:space="preserve">7039706</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J238">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801762</t>
+          <t xml:space="preserve">311843431</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-09</t>
+          <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemarksvej 43</t>
+          <t xml:space="preserve">Thorvalds Vænge 9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">286845</t>
+          <t xml:space="preserve">5462279</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -17910,11 +17910,11 @@
         </is>
       </c>
       <c r="J239">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843430</t>
+          <t xml:space="preserve">311859602</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-08</t>
+          <t xml:space="preserve">2035-10-02</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,30 +17966,30 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrelunden 20</t>
+          <t xml:space="preserve">Paarupvej 21</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2654536</t>
+          <t xml:space="preserve">9552027</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J240">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843436</t>
+          <t xml:space="preserve">311864279</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-08</t>
+          <t xml:space="preserve">2035-10-24</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,30 +18041,30 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrelunden 20</t>
+          <t xml:space="preserve">Paarupvej 21</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">7039706</t>
+          <t xml:space="preserve">9552027</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J241">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843431</t>
+          <t xml:space="preserve">311864280</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-08</t>
+          <t xml:space="preserve">2035-10-24</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,30 +18116,30 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvalds Vænge 9</t>
+          <t xml:space="preserve">Paarupvej 21A</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462279</t>
+          <t xml:space="preserve">2619528</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311859602</t>
+          <t xml:space="preserve">311864283</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-02</t>
+          <t xml:space="preserve">2035-10-24</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,40 +18191,40 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paarupvej 21</t>
+          <t xml:space="preserve">Mindelundsvej 44</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552027</t>
+          <t xml:space="preserve">2659338</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J243">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864279</t>
+          <t xml:space="preserve">311867914</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-24</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,40 +18266,40 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paarupvej 21</t>
+          <t xml:space="preserve">Bangs Boder 7</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552027</t>
+          <t xml:space="preserve">7591700</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J244">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864280</t>
+          <t xml:space="preserve">311869561</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-24</t>
+          <t xml:space="preserve">2035-11-21</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,30 +18341,30 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paarupvej 21A</t>
+          <t xml:space="preserve">Fengersvej 6</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2619528</t>
+          <t xml:space="preserve">9552597</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J245">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864283</t>
+          <t xml:space="preserve">311869608</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-24</t>
+          <t xml:space="preserve">2035-11-21</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,40 +18416,40 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mindelundsvej 44</t>
+          <t xml:space="preserve">Kildemosevej 20</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2659338</t>
+          <t xml:space="preserve">10088928</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J246">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867914</t>
+          <t xml:space="preserve">311873954</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-12</t>
+          <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangs Boder 7</t>
+          <t xml:space="preserve">Kochsgade 29</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,30 +18501,30 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">7591700</t>
+          <t xml:space="preserve">5475237</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J247">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869561</t>
+          <t xml:space="preserve">311873959</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-21</t>
+          <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,30 +18566,30 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fengersvej 6</t>
+          <t xml:space="preserve">Kochsgade 29</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552597</t>
+          <t xml:space="preserve">5475237</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J248">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869608</t>
+          <t xml:space="preserve">311873959</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-21</t>
+          <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18636,35 +18636,35 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">430</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemosevej 20</t>
+          <t xml:space="preserve">Volstrupvej 16</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5750</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">10088928</t>
+          <t xml:space="preserve">7458968</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J249">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873954</t>
+          <t xml:space="preserve">311873923</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18716,30 +18716,30 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kochsgade 29</t>
+          <t xml:space="preserve">Væddeløbsvej 4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5475237</t>
+          <t xml:space="preserve">2622776</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J250">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873959</t>
+          <t xml:space="preserve">311873939</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18791,30 +18791,30 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kochsgade 29</t>
+          <t xml:space="preserve">Væddeløbsvej 4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5475237</t>
+          <t xml:space="preserve">2622776</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J251">
-        <v>163</v>
+        <v>233</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873959</t>
+          <t xml:space="preserve">311873940</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18861,22 +18861,22 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">430</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volstrupvej 16</t>
+          <t xml:space="preserve">Østergade 55B</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5750</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">7458968</t>
+          <t xml:space="preserve">5475522</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -18885,11 +18885,11 @@
         </is>
       </c>
       <c r="J252">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873923</t>
+          <t xml:space="preserve">311873946</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18941,30 +18941,30 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Væddeløbsvej 4</t>
+          <t xml:space="preserve">Smedebakken 26</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2622776</t>
+          <t xml:space="preserve">2639201</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873939</t>
+          <t xml:space="preserve">311878261</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-17</t>
+          <t xml:space="preserve">2036-01-23</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,30 +19016,30 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Væddeløbsvej 4</t>
+          <t xml:space="preserve">Georgsgade 61A</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2622776</t>
+          <t xml:space="preserve">5456649</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J254">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873940</t>
+          <t xml:space="preserve">311881928</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-17</t>
+          <t xml:space="preserve">2036-02-13</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,30 +19091,30 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 55B</t>
+          <t xml:space="preserve">Rismarksvej 80A</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5475522</t>
+          <t xml:space="preserve">5462930</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J255">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873946</t>
+          <t xml:space="preserve">311881924</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-17</t>
+          <t xml:space="preserve">2036-02-13</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,30 +19166,30 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 26</t>
+          <t xml:space="preserve">Rismarksvej 80A</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2639201</t>
+          <t xml:space="preserve">5462930</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J256">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878261</t>
+          <t xml:space="preserve">311881925</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-23</t>
+          <t xml:space="preserve">2036-02-13</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,30 +19241,30 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georgsgade 61A</t>
+          <t xml:space="preserve">Rismarksvej 80A</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5456649</t>
+          <t xml:space="preserve">5462930</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J257">
-        <v>168</v>
+        <v>98</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881928</t>
+          <t xml:space="preserve">311881925</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19316,30 +19316,30 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rismarksvej 80A</t>
+          <t xml:space="preserve">Svenstrupvej 20</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462930</t>
+          <t xml:space="preserve">2626850</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J258">
-        <v>247</v>
+        <v>133</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881924</t>
+          <t xml:space="preserve">311881927</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19391,30 +19391,30 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rismarksvej 80A</t>
+          <t xml:space="preserve">Svenstrupvej 20</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462930</t>
+          <t xml:space="preserve">2626850</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J259">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881925</t>
+          <t xml:space="preserve">311881927</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19466,30 +19466,30 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rismarksvej 80A</t>
+          <t xml:space="preserve">Døckerslundsvej 188</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462930</t>
+          <t xml:space="preserve">5461709</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J260">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881925</t>
+          <t xml:space="preserve">311886395</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-13</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,30 +19541,30 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svenstrupvej 20</t>
+          <t xml:space="preserve">Døckerslundsvej 190</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2626850</t>
+          <t xml:space="preserve">5461709</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J261">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881927</t>
+          <t xml:space="preserve">311886395</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-13</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,30 +19616,30 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svenstrupvej 20</t>
+          <t xml:space="preserve">Roesskovsvej 125</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2626850</t>
+          <t xml:space="preserve">5463689</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J262">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881927</t>
+          <t xml:space="preserve">311894848</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-13</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,30 +19691,30 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døckerslundsvej 188</t>
+          <t xml:space="preserve">Roesskovsvej 125</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461709</t>
+          <t xml:space="preserve">5463689</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J263">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886395</t>
+          <t xml:space="preserve">311894848</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,30 +19766,30 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døckerslundsvej 190</t>
+          <t xml:space="preserve">Roesskovsvej 125</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461709</t>
+          <t xml:space="preserve">5463689</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J264">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886395</t>
+          <t xml:space="preserve">311894848</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19856,11 +19856,11 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J265">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -19926,20 +19926,20 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5463689</t>
+          <t xml:space="preserve">5463700</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J266">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894848</t>
+          <t xml:space="preserve">311894849</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -20001,20 +20001,20 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5463689</t>
+          <t xml:space="preserve">5463700</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J267">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894848</t>
+          <t xml:space="preserve">311894849</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roesskovsvej 125</t>
+          <t xml:space="preserve">Roesskovsvej 125D</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,12 +20076,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">5463689</t>
+          <t xml:space="preserve">5463700</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J268">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894848</t>
+          <t xml:space="preserve">311894849</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roesskovsvej 125</t>
+          <t xml:space="preserve">Roesskovsvej 125D</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20156,11 +20156,11 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J269">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -20216,30 +20216,30 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roesskovsvej 125</t>
+          <t xml:space="preserve">Kong Georgs Vej 31</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5463700</t>
+          <t xml:space="preserve">5476057</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J270">
-        <v>169</v>
+        <v>119</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894849</t>
+          <t xml:space="preserve">311900002</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-05-08</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,30 +20291,30 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roesskovsvej 125D</t>
+          <t xml:space="preserve">Kong Georgs Vej 31</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5463700</t>
+          <t xml:space="preserve">5476057</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J271">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894849</t>
+          <t xml:space="preserve">311900002</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-05-08</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,30 +20366,30 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roesskovsvej 125D</t>
+          <t xml:space="preserve">Rødegårdsvej 196</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5463700</t>
+          <t xml:space="preserve">5460566</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J272">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894849</t>
+          <t xml:space="preserve">311899992</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-05-08</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,30 +20441,30 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Georgs Vej 31</t>
+          <t xml:space="preserve">Rødegårdsvej 204</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">5476057</t>
+          <t xml:space="preserve">5460566</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="J273">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900002</t>
+          <t xml:space="preserve">311899994</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20516,30 +20516,30 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Georgs Vej 31</t>
+          <t xml:space="preserve">Rødegårdsvej 206</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5476057</t>
+          <t xml:space="preserve">5460566</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J274">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900002</t>
+          <t xml:space="preserve">311899993</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødegårdsvej 196</t>
+          <t xml:space="preserve">Stærmosegårdsvej 53</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20606,15 +20606,15 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J275">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899992</t>
+          <t xml:space="preserve">311899995</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødegårdsvej 204</t>
+          <t xml:space="preserve">Stærmosegårdsvej 55</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20681,15 +20681,15 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J276">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899994</t>
+          <t xml:space="preserve">311899991</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20741,30 +20741,30 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødegårdsvej 206</t>
+          <t xml:space="preserve">Sædekildegårdvej 6</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5460566</t>
+          <t xml:space="preserve">2606267</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J277">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899993</t>
+          <t xml:space="preserve">311899988</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20816,30 +20816,30 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stærmosegårdsvej 53</t>
+          <t xml:space="preserve">Gillestedvej 15</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5460566</t>
+          <t xml:space="preserve">5461129</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J278">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899995</t>
+          <t xml:space="preserve">311903989</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-08</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20891,30 +20891,30 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stærmosegårdsvej 55</t>
+          <t xml:space="preserve">Møllemarksvej 71C</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">5460566</t>
+          <t xml:space="preserve">5458778</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J279">
-        <v>245</v>
+        <v>118</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899991</t>
+          <t xml:space="preserve">311904053</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-08</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20966,30 +20966,30 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sædekildegårdvej 6</t>
+          <t xml:space="preserve">Rømersvej 1A</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2606267</t>
+          <t xml:space="preserve">5459047</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J280">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899988</t>
+          <t xml:space="preserve">311907589</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20999,7 +20999,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-08</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21041,30 +21041,30 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gillestedvej 15</t>
+          <t xml:space="preserve">Windelsvej 145</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">5461129</t>
+          <t xml:space="preserve">9552644</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J281">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903989</t>
+          <t xml:space="preserve">311907597</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21116,30 +21116,30 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemarksvej 71C</t>
+          <t xml:space="preserve">Bergendals Allé 25</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">5458778</t>
+          <t xml:space="preserve">2610434</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J282">
-        <v>118</v>
+        <v>246</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904053</t>
+          <t xml:space="preserve">311908678</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-17</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21191,30 +21191,30 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rømersvej 1A</t>
+          <t xml:space="preserve">Falen 97</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">5459047</t>
+          <t xml:space="preserve">10088928</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J283">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907589</t>
+          <t xml:space="preserve">311908769</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-06-17</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21266,30 +21266,30 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windelsvej 145</t>
+          <t xml:space="preserve">Galopbanevej 35</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5250</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552644</t>
+          <t xml:space="preserve">2625289</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J284">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907597</t>
+          <t xml:space="preserve">311908778</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-06-17</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,17 +21341,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergendals Allé 25</t>
+          <t xml:space="preserve">Ærtebjerghaven 34</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5270</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2610434</t>
+          <t xml:space="preserve">8037557</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -21360,11 +21360,11 @@
         </is>
       </c>
       <c r="J285">
-        <v>246</v>
+        <v>98</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908678</t>
+          <t xml:space="preserve">311908482</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falen 97</t>
+          <t xml:space="preserve">Schacksgade 41</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21426,20 +21426,20 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">10088928</t>
+          <t xml:space="preserve">5464777</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J286">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908769</t>
+          <t xml:space="preserve">311911798</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-17</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21491,30 +21491,30 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galopbanevej 35</t>
+          <t xml:space="preserve">Læssøegade 45</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2625289</t>
+          <t xml:space="preserve">5468388</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J287">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908778</t>
+          <t xml:space="preserve">311912051</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-17</t>
+          <t xml:space="preserve">2036-07-01</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,40 +21566,40 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ærtebjerghaven 34</t>
+          <t xml:space="preserve">Claus Bergs Gade 3D</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">8037557</t>
+          <t xml:space="preserve">5456147</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J288">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908482</t>
+          <t xml:space="preserve">311912425</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-17</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schacksgade 41</t>
+          <t xml:space="preserve">Claus Bergs Gade 3E</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -21651,30 +21651,30 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5464777</t>
+          <t xml:space="preserve">5456147</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J289">
-        <v>93</v>
+        <v>233</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911798</t>
+          <t xml:space="preserve">311912425</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21716,17 +21716,17 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Læssøegade 45</t>
+          <t xml:space="preserve">Overgade 48</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">5468388</t>
+          <t xml:space="preserve">5456147</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -21735,21 +21735,21 @@
         </is>
       </c>
       <c r="J290">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912051</t>
+          <t xml:space="preserve">311912425</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-01</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claus Bergs Gade 3D</t>
+          <t xml:space="preserve">Sortebrødre Stræde 5D</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -21806,11 +21806,11 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J291">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -21866,40 +21866,40 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claus Bergs Gade 3E</t>
+          <t xml:space="preserve">Ejby Kirkevej 15</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5456147</t>
+          <t xml:space="preserve">5465079</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J292">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912425</t>
+          <t xml:space="preserve">311912853</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-07-04</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 48</t>
+          <t xml:space="preserve">Bjergegade 15</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21951,30 +21951,30 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">5456147</t>
+          <t xml:space="preserve">5452403</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J293">
-        <v>68</v>
+        <v>198</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912425</t>
+          <t xml:space="preserve">311923048</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22016,40 +22016,40 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sortebrødre Stræde 5D</t>
+          <t xml:space="preserve">Demantsvej 30</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">5456147</t>
+          <t xml:space="preserve">2611864</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J294">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912425</t>
+          <t xml:space="preserve">311923088</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -22091,30 +22091,30 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Kirkevej 15</t>
+          <t xml:space="preserve">Middelfartvej 180</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5465079</t>
+          <t xml:space="preserve">5463690</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J295">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912853</t>
+          <t xml:space="preserve">311923077</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-04</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,30 +22166,30 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjergegade 15</t>
+          <t xml:space="preserve">Middelfartvej 182</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5200</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5452403</t>
+          <t xml:space="preserve">5463690</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J296">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923048</t>
+          <t xml:space="preserve">311923076</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -22241,30 +22241,30 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demantsvej 30</t>
+          <t xml:space="preserve">Præstevej 10</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5210</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2611864</t>
+          <t xml:space="preserve">2630140</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J297">
-        <v>181</v>
+        <v>123</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923088</t>
+          <t xml:space="preserve">311923056</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22316,30 +22316,30 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middelfartvej 180</t>
+          <t xml:space="preserve">Tornbjergvej 1</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5220</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">5463690</t>
+          <t xml:space="preserve">8167174</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J298">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923077</t>
+          <t xml:space="preserve">311922996</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22391,30 +22391,30 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middelfartvej 182</t>
+          <t xml:space="preserve">Rødegårdsvej 164</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200</t>
+          <t xml:space="preserve">5230</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">5463690</t>
+          <t xml:space="preserve">5466521</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J299">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923076</t>
+          <t xml:space="preserve">311923222</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -22466,30 +22466,30 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstevej 10</t>
+          <t xml:space="preserve">Roersvej 10</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">5210</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630140</t>
+          <t xml:space="preserve">5454020</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J300">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923056</t>
+          <t xml:space="preserve">311924339</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-08</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -22541,30 +22541,30 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tornbjergvej 1</t>
+          <t xml:space="preserve">Roersvej 10</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">8167174</t>
+          <t xml:space="preserve">5454020</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J301">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922996</t>
+          <t xml:space="preserve">311924339</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-08</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -22616,17 +22616,17 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødegårdsvej 164</t>
+          <t xml:space="preserve">Roersvej 8B</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5230</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5466521</t>
+          <t xml:space="preserve">5454020</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -22635,11 +22635,11 @@
         </is>
       </c>
       <c r="J302">
-        <v>101</v>
+        <v>171</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923222</t>
+          <t xml:space="preserve">311924340</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-09-08</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22691,17 +22691,17 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roersvej 10</t>
+          <t xml:space="preserve">Solbakken 23</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5260</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">5454020</t>
+          <t xml:space="preserve">2611888</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -22710,11 +22710,11 @@
         </is>
       </c>
       <c r="J303">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924339</t>
+          <t xml:space="preserve">311925906</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22724,7 +22724,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-08</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -22766,30 +22766,30 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roersvej 10</t>
+          <t xml:space="preserve">Østbirkvej 21</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5454020</t>
+          <t xml:space="preserve">9552403</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J304">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924339</t>
+          <t xml:space="preserve">311925922</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-08</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22841,30 +22841,30 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roersvej 8B</t>
+          <t xml:space="preserve">Amaliehaven 55</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000</t>
+          <t xml:space="preserve">5240</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5454020</t>
+          <t xml:space="preserve">1330026</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J305">
-        <v>171</v>
+        <v>88</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924340</t>
+          <t xml:space="preserve">311926373</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-08</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -22916,30 +22916,30 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbakken 23</t>
+          <t xml:space="preserve">Unsgaardsgade 1A</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2611888</t>
+          <t xml:space="preserve">5475500</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J306">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925906</t>
+          <t xml:space="preserve">311931347</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-15</t>
+          <t xml:space="preserve">2036-10-12</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -22991,30 +22991,30 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østbirkvej 21</t>
+          <t xml:space="preserve">Risingsvej 25</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">9552403</t>
+          <t xml:space="preserve">5474054</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J307">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925922</t>
+          <t xml:space="preserve">311931475</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-15</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -23066,30 +23066,30 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amaliehaven 55</t>
+          <t xml:space="preserve">Risingsvej 25A</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">5240</t>
+          <t xml:space="preserve">5000</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">1330026</t>
+          <t xml:space="preserve">5474054</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J308">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926373</t>
+          <t xml:space="preserve">311931476</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-17</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
